--- a/output/2026-10-14/enriched_analysis.xlsx
+++ b/output/2026-10-14/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.275</v>
+        <v>2.241</v>
       </c>
       <c r="W2" t="n">
-        <v>2770</v>
+        <v>2811</v>
       </c>
       <c r="X2" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.834</v>
+        <v>0.829</v>
       </c>
       <c r="W3" t="n">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="X3" t="n">
         <v>136</v>
@@ -1396,10 +1396,10 @@
         <v>0.021</v>
       </c>
       <c r="W4" t="n">
-        <v>3406</v>
+        <v>3433</v>
       </c>
       <c r="X4" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
         <v>18</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="W5" t="n">
-        <v>2958</v>
+        <v>3031</v>
       </c>
       <c r="X5" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="Y5" t="n">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.025</v>
+        <v>1.047</v>
       </c>
       <c r="W6" t="n">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="X6" t="n">
-        <v>88.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="Y6" t="n">
         <v>111</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.51</v>
+        <v>0.513</v>
       </c>
       <c r="W7" t="n">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="X7" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="Y7" t="n">
         <v>19</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.223</v>
+        <v>1.203</v>
       </c>
       <c r="W8" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="X8" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Y8" t="n">
         <v>22</v>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.329</v>
+        <v>0.322</v>
       </c>
       <c r="W9" t="n">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="X9" t="n">
-        <v>9.140000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="Y9" t="n">
         <v>7</v>
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1.187</v>
+        <v>1.194</v>
       </c>
       <c r="W10" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X10" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="Y10" t="n">
         <v>17</v>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.457</v>
+        <v>1.443</v>
       </c>
       <c r="W11" t="n">
-        <v>9284</v>
+        <v>9377</v>
       </c>
       <c r="X11" t="n">
-        <v>1563</v>
+        <v>1579</v>
       </c>
       <c r="Y11" t="n">
         <v>-53</v>
@@ -3252,7 +3252,7 @@
         <v>0.047</v>
       </c>
       <c r="W12" t="n">
-        <v>15232</v>
+        <v>15249</v>
       </c>
       <c r="X12" t="n">
         <v>38.8</v>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="W14" t="n">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="X14" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3948,10 +3948,10 @@
         <v>0.049</v>
       </c>
       <c r="W15" t="n">
-        <v>1693</v>
+        <v>1673</v>
       </c>
       <c r="X15" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="Y15" t="n">
         <v>55</v>
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
       <c r="W16" t="n">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="X16" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Y16" t="n">
         <v>19</v>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1.981</v>
+        <v>1.959</v>
       </c>
       <c r="W17" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="W18" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="X18" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
       </c>
       <c r="Y18" t="n">
         <v>2</v>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.241</v>
+        <v>0.233</v>
       </c>
       <c r="W19" t="n">
-        <v>1428</v>
+        <v>1476</v>
       </c>
       <c r="X19" t="n">
-        <v>24.3</v>
+        <v>25.1</v>
       </c>
       <c r="Y19" t="n">
         <v>8</v>
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.132</v>
+        <v>0.126</v>
       </c>
       <c r="W20" t="n">
-        <v>2383</v>
+        <v>2494</v>
       </c>
       <c r="X20" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="Y20" t="n">
         <v>-3</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>2523</v>
+        <v>2542</v>
       </c>
       <c r="X21" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>3.179</v>
+        <v>3.144</v>
       </c>
       <c r="W22" t="n">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="X22" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="Y22" t="n">
         <v>30</v>
@@ -5792,10 +5792,10 @@
         <v>0.178</v>
       </c>
       <c r="W23" t="n">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="X23" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="Y23" t="n">
         <v>3</v>
@@ -6021,13 +6021,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.102</v>
+        <v>0.101</v>
       </c>
       <c r="W24" t="n">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="X24" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="Y24" t="n">
         <v>17</v>
@@ -6247,13 +6247,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.139</v>
+        <v>0.135</v>
       </c>
       <c r="W25" t="n">
-        <v>1523</v>
+        <v>1568</v>
       </c>
       <c r="X25" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="Y25" t="n">
         <v>152</v>
@@ -6479,13 +6479,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="W26" t="n">
-        <v>2088</v>
+        <v>2112</v>
       </c>
       <c r="X26" t="n">
-        <v>97</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Y26" t="n">
         <v>13</v>
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.344</v>
+        <v>0.337</v>
       </c>
       <c r="W27" t="n">
-        <v>940</v>
+        <v>959</v>
       </c>
       <c r="X27" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="Y27" t="n">
         <v>13</v>
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="W28" t="n">
-        <v>1712</v>
+        <v>1745</v>
       </c>
       <c r="X28" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Y28" t="n">
         <v>-48</v>
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="W29" t="n">
-        <v>1588</v>
+        <v>1628</v>
       </c>
       <c r="X29" t="n">
-        <v>36.4</v>
+        <v>37.4</v>
       </c>
       <c r="Y29" t="n">
         <v>20</v>
@@ -7407,13 +7407,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
       <c r="W30" t="n">
-        <v>59404</v>
+        <v>59791</v>
       </c>
       <c r="X30" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="Y30" t="n">
         <v>5</v>
@@ -7639,13 +7639,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.542</v>
+        <v>0.54</v>
       </c>
       <c r="W31" t="n">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="X31" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="Y31" t="n">
         <v>13</v>
@@ -7874,10 +7874,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>55508</v>
+        <v>55776</v>
       </c>
       <c r="X32" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="Y32" t="n">
         <v>5</v>
@@ -8106,7 +8106,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="X33" t="n">
         <v>10.8</v>
@@ -8335,13 +8335,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>1.633</v>
+        <v>1.597</v>
       </c>
       <c r="W34" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="X34" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="Y34" t="n">
         <v>-14</v>
@@ -8567,13 +8567,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.16</v>
+        <v>0.153</v>
       </c>
       <c r="W35" t="n">
-        <v>3986</v>
+        <v>4189</v>
       </c>
       <c r="X35" t="n">
-        <v>7.51</v>
+        <v>7.9</v>
       </c>
       <c r="Y35" t="n">
         <v>2</v>
@@ -8799,13 +8799,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>1.102</v>
+        <v>1.12</v>
       </c>
       <c r="W36" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="X36" t="n">
-        <v>5.27</v>
+        <v>5.17</v>
       </c>
       <c r="Y36" t="n">
         <v>31</v>
@@ -9027,13 +9027,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.263</v>
+        <v>0.26</v>
       </c>
       <c r="W37" t="n">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="X37" t="n">
-        <v>26.9</v>
+        <v>27.3</v>
       </c>
       <c r="Y37" t="n">
         <v>9</v>
@@ -9261,7 +9261,7 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
-        <v>5.87</v>
+        <v>5.58</v>
       </c>
       <c r="Y38" t="n">
         <v>-68</v>
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>1.075</v>
+        <v>1.082</v>
       </c>
       <c r="W39" t="n">
-        <v>1849</v>
+        <v>1838</v>
       </c>
       <c r="X39" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Y39" t="n">
         <v>12</v>
@@ -9722,10 +9722,10 @@
         <v>0.01</v>
       </c>
       <c r="W40" t="n">
-        <v>14720</v>
+        <v>15097</v>
       </c>
       <c r="X40" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="Y40" t="n">
         <v>28</v>
@@ -9951,13 +9951,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="W41" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="X41" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y41" t="n">
         <v>12</v>
@@ -10186,10 +10186,10 @@
         <v>0.004</v>
       </c>
       <c r="W42" t="n">
-        <v>49527</v>
+        <v>47866</v>
       </c>
       <c r="X42" t="n">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="Y42" t="n">
         <v>26</v>
@@ -10418,10 +10418,10 @@
         <v>0.374</v>
       </c>
       <c r="W43" t="n">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="X43" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
       <c r="Y43" t="n">
         <v>21</v>
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>1.876</v>
+        <v>1.845</v>
       </c>
       <c r="W45" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="n">
@@ -11109,13 +11109,13 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.524</v>
+        <v>0.52</v>
       </c>
       <c r="W46" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="X46" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="Y46" t="n">
         <v>21</v>
@@ -11344,10 +11344,10 @@
         <v>0.042</v>
       </c>
       <c r="W47" t="n">
-        <v>1646</v>
+        <v>1633</v>
       </c>
       <c r="X47" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="Y47" t="n">
         <v>10</v>
@@ -11573,10 +11573,10 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>4.621</v>
+        <v>4.437</v>
       </c>
       <c r="W48" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="n">
@@ -11803,13 +11803,13 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.512</v>
+        <v>0.509</v>
       </c>
       <c r="W49" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X49" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="Y49" t="n">
         <v>-44</v>
@@ -11963,16 +11963,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -11980,40 +11980,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H50" t="n">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="I50" t="n">
-        <v>24.27</v>
+        <v>447.2</v>
       </c>
       <c r="J50" t="n">
-        <v>27.53</v>
+        <v>349.57</v>
       </c>
       <c r="K50" t="n">
-        <v>-11.8</v>
+        <v>27.9</v>
       </c>
       <c r="L50" t="n">
-        <v>61.81</v>
+        <v>70.55</v>
       </c>
       <c r="M50" t="n">
-        <v>0.65</v>
+        <v>31.6</v>
       </c>
       <c r="N50" t="n">
-        <v>6470400</v>
+        <v>315995536</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>6470400</v>
+        <v>315995536</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -12035,52 +12035,52 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>0.252</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="W50" t="n">
-        <v>257</v>
+        <v>3907</v>
       </c>
       <c r="X50" t="n">
-        <v>13.5</v>
+        <v>27.3</v>
       </c>
       <c r="Y50" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.79</v>
+        <v>127</v>
       </c>
       <c r="AA50" t="n">
-        <v>-30</v>
+        <v>-14</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.21</v>
+        <v>6.41</v>
       </c>
       <c r="AC50" t="n">
-        <v>18</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.32</v>
+        <v>1.05</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.83</v>
+        <v>21</v>
       </c>
       <c r="AG50" t="n">
-        <v>27.11</v>
+        <v>443.07</v>
       </c>
       <c r="AH50" t="n">
-        <v>31.44</v>
+        <v>433.75</v>
       </c>
       <c r="AI50" t="n">
-        <v>-19</v>
+        <v>7.2</v>
       </c>
       <c r="AJ50" t="n">
-        <v>27.53361702127659</v>
+        <v>349.5746258337085</v>
       </c>
       <c r="AK50" t="n">
-        <v>-11.9</v>
+        <v>27.9</v>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
@@ -12094,12 +12094,12 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
@@ -12108,10 +12108,10 @@
         </is>
       </c>
       <c r="AQ50" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AR50" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AS50" t="n">
         <v>14</v>
@@ -12126,25 +12126,25 @@
         <v>6</v>
       </c>
       <c r="AW50" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>925400</v>
+        <v>464</v>
       </c>
       <c r="BA50" t="n">
-        <v>4267650</v>
+        <v>213764633</v>
       </c>
       <c r="BB50" t="n">
-        <v>6470400</v>
+        <v>213764633</v>
       </c>
       <c r="BC50" t="n">
-        <v>6470400</v>
+        <v>315995536</v>
       </c>
       <c r="BD50" t="n">
         <v>0</v>
@@ -12180,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="BO50" t="n">
-        <v>4267650</v>
+        <v>213764633</v>
       </c>
       <c r="BP50" t="n">
         <v>1</v>
@@ -12195,12 +12195,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -12212,107 +12212,103 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F51" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="J51" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N51" t="n">
+        <v>23479616</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>23479616</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
         <v>25</v>
       </c>
-      <c r="H51" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I51" t="n">
-        <v>447.2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>349.57</v>
-      </c>
-      <c r="K51" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="L51" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="M51" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="N51" t="n">
-        <v>315995536</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>315995536</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S51" t="b">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>11</v>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>0.824</v>
+        <v>0.695</v>
       </c>
       <c r="W51" t="n">
-        <v>3837</v>
+        <v>338</v>
       </c>
       <c r="X51" t="n">
-        <v>26.8</v>
+        <v>1091</v>
       </c>
       <c r="Y51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>127</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="n">
-        <v>-14</v>
+        <v>-98</v>
       </c>
       <c r="AB51" t="n">
-        <v>6.41</v>
+        <v>0.01</v>
       </c>
       <c r="AC51" t="n">
-        <v>9.890000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="n">
-        <v>443.07</v>
+        <v>12.83</v>
       </c>
       <c r="AH51" t="n">
-        <v>433.75</v>
+        <v>12.91</v>
       </c>
       <c r="AI51" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>349.5746258337085</v>
+        <v>12.85608234597773</v>
       </c>
       <c r="AK51" t="n">
-        <v>27.9</v>
+        <v>-3.2</v>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
@@ -12326,57 +12322,57 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ51" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AR51" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AS51" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
       <c r="AU51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW51" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AX51" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AY51" t="n">
         <v>0</v>
       </c>
       <c r="AZ51" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>213764633</v>
+        <v>2496337</v>
       </c>
       <c r="BB51" t="n">
-        <v>213764633</v>
+        <v>16559572</v>
       </c>
       <c r="BC51" t="n">
-        <v>315995536</v>
+        <v>23479616</v>
       </c>
       <c r="BD51" t="n">
         <v>0</v>
@@ -12412,7 +12408,7 @@
         <v>0</v>
       </c>
       <c r="BO51" t="n">
-        <v>213764633</v>
+        <v>2496337</v>
       </c>
       <c r="BP51" t="n">
         <v>1</v>
@@ -12427,12 +12423,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -12444,40 +12440,40 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>12.44</v>
+        <v>424.45</v>
       </c>
       <c r="J52" t="n">
-        <v>12.86</v>
+        <v>473.17</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.3</v>
+        <v>-10.3</v>
       </c>
       <c r="L52" t="n">
-        <v>69.12</v>
+        <v>56.22</v>
       </c>
       <c r="M52" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="N52" t="n">
-        <v>23479616</v>
+        <v>23279819</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>23479616</v>
+        <v>23279819</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -12491,56 +12487,60 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>0.669</v>
+        <v>0.044</v>
       </c>
       <c r="W52" t="n">
-        <v>351</v>
+        <v>5241</v>
       </c>
       <c r="X52" t="n">
-        <v>1132</v>
+        <v>27.2</v>
       </c>
       <c r="Y52" t="n">
-        <v>-61</v>
-      </c>
-      <c r="Z52" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>59</v>
+      </c>
       <c r="AA52" t="n">
-        <v>-98</v>
+        <v>-52</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.01</v>
+        <v>3.48</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.46</v>
+        <v>24.3</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="AE52" t="b">
         <v>1</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
+      <c r="AF52" t="n">
+        <v>7</v>
+      </c>
       <c r="AG52" t="n">
-        <v>12.83</v>
+        <v>479.42</v>
       </c>
       <c r="AH52" t="n">
-        <v>12.91</v>
+        <v>548.23</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.6</v>
+        <v>-16.8</v>
       </c>
       <c r="AJ52" t="n">
-        <v>12.85608234597773</v>
+        <v>473.1670528455285</v>
       </c>
       <c r="AK52" t="n">
-        <v>-3.2</v>
+        <v>-10.3</v>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
@@ -12559,22 +12559,22 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AQ52" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="AR52" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AS52" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AT52" t="n">
         <v>0</v>
@@ -12583,13 +12583,13 @@
         <v>0</v>
       </c>
       <c r="AV52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW52" t="n">
         <v>4</v>
       </c>
-      <c r="AW52" t="n">
-        <v>22</v>
-      </c>
       <c r="AX52" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AY52" t="n">
         <v>0</v>
@@ -12598,13 +12598,13 @@
         <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>2496337</v>
+        <v>11585069</v>
       </c>
       <c r="BB52" t="n">
-        <v>16559572</v>
+        <v>23279819</v>
       </c>
       <c r="BC52" t="n">
-        <v>23479616</v>
+        <v>23279819</v>
       </c>
       <c r="BD52" t="n">
         <v>0</v>
@@ -12640,10 +12640,10 @@
         <v>0</v>
       </c>
       <c r="BO52" t="n">
-        <v>2496337</v>
+        <v>11585069</v>
       </c>
       <c r="BP52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ52" t="n">
         <v>0</v>
@@ -12655,12 +12655,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -12672,40 +12672,40 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G53" t="n">
         <v>12</v>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>424.45</v>
+        <v>3.26</v>
       </c>
       <c r="J53" t="n">
-        <v>473.17</v>
+        <v>2.82</v>
       </c>
       <c r="K53" t="n">
-        <v>-10.3</v>
+        <v>15.6</v>
       </c>
       <c r="L53" t="n">
-        <v>56.22</v>
+        <v>64.45</v>
       </c>
       <c r="M53" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="N53" t="n">
-        <v>23279819</v>
+        <v>20159573</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>23279819</v>
+        <v>20159573</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -12719,60 +12719,54 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="V53" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="W53" t="n">
-        <v>5238</v>
-      </c>
-      <c r="X53" t="n">
-        <v>27.2</v>
-      </c>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z53" t="n">
-        <v>59</v>
+        <v>0.98</v>
       </c>
       <c r="AA53" t="n">
-        <v>-52</v>
+        <v>-86</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.48</v>
+        <v>-0.03</v>
       </c>
       <c r="AC53" t="n">
-        <v>24.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.26</v>
+        <v>1.58</v>
       </c>
       <c r="AE53" t="b">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>7</v>
+        <v>14.22</v>
       </c>
       <c r="AG53" t="n">
-        <v>479.42</v>
+        <v>2.91</v>
       </c>
       <c r="AH53" t="n">
-        <v>548.23</v>
+        <v>3.16</v>
       </c>
       <c r="AI53" t="n">
-        <v>-16.8</v>
+        <v>-3.6</v>
       </c>
       <c r="AJ53" t="n">
-        <v>473.1670528455285</v>
+        <v>2.817550384346611</v>
       </c>
       <c r="AK53" t="n">
-        <v>-10.3</v>
+        <v>15.7</v>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
@@ -12781,32 +12775,32 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AR53" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AS53" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AT53" t="n">
         <v>0</v>
@@ -12815,13 +12809,13 @@
         <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY53" t="n">
         <v>0</v>
@@ -12830,13 +12824,13 @@
         <v>0</v>
       </c>
       <c r="BA53" t="n">
-        <v>11585069</v>
+        <v>20159573</v>
       </c>
       <c r="BB53" t="n">
-        <v>23279819</v>
+        <v>20159573</v>
       </c>
       <c r="BC53" t="n">
-        <v>23279819</v>
+        <v>20159573</v>
       </c>
       <c r="BD53" t="n">
         <v>0</v>
@@ -12872,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="BO53" t="n">
-        <v>11585069</v>
+        <v>20159573</v>
       </c>
       <c r="BP53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ53" t="n">
         <v>0</v>
@@ -12887,182 +12881,188 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="J54" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="L54" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6470400</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>6470400</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>9</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="W54" t="n">
+        <v>268</v>
+      </c>
+      <c r="X54" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>27.53361702127659</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ54" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>56</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV54" t="n">
         <v>6</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G54" t="n">
-        <v>12</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K54" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="L54" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="N54" t="n">
-        <v>20159573</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>20159573</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S54" t="b">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>-86</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>2.817550384346611</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="AP54" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>1</v>
-      </c>
       <c r="AW54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AX54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AY54" t="n">
         <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>925400</v>
       </c>
       <c r="BA54" t="n">
-        <v>20159573</v>
+        <v>4267650</v>
       </c>
       <c r="BB54" t="n">
-        <v>20159573</v>
+        <v>6470400</v>
       </c>
       <c r="BC54" t="n">
-        <v>20159573</v>
+        <v>6470400</v>
       </c>
       <c r="BD54" t="n">
         <v>0</v>
@@ -13098,7 +13098,7 @@
         <v>0</v>
       </c>
       <c r="BO54" t="n">
-        <v>20159573</v>
+        <v>4267650</v>
       </c>
       <c r="BP54" t="n">
         <v>1</v>
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="V55" t="n">
-        <v>0.231</v>
+        <v>0.229</v>
       </c>
       <c r="W55" t="n">
-        <v>1730</v>
+        <v>1743</v>
       </c>
       <c r="X55" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="Y55" t="n">
         <v>-3</v>
@@ -13420,7 +13420,7 @@
         <v>0.042</v>
       </c>
       <c r="W56" t="n">
-        <v>3213</v>
+        <v>3224</v>
       </c>
       <c r="X56" t="n">
         <v>19.1</v>
@@ -13649,13 +13649,13 @@
         </is>
       </c>
       <c r="V57" t="n">
-        <v>0.372</v>
+        <v>0.366</v>
       </c>
       <c r="W57" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="X57" t="n">
-        <v>93.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="Y57" t="n">
         <v>246</v>
@@ -13881,13 +13881,13 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="W58" t="n">
-        <v>7493</v>
+        <v>7682</v>
       </c>
       <c r="X58" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="Y58" t="n">
         <v>25</v>
@@ -14109,13 +14109,13 @@
         </is>
       </c>
       <c r="V59" t="n">
-        <v>0.332</v>
+        <v>0.328</v>
       </c>
       <c r="W59" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="X59" t="n">
-        <v>57.7</v>
+        <v>58.4</v>
       </c>
       <c r="Y59" t="n">
         <v>13</v>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>0.198</v>
+        <v>0.2</v>
       </c>
       <c r="W61" t="n">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="X61" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y61" t="n">
         <v>-1</v>
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="V62" t="n">
-        <v>0.483</v>
+        <v>0.474</v>
       </c>
       <c r="W62" t="n">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="X62" t="n">
-        <v>41.6</v>
+        <v>42.4</v>
       </c>
       <c r="Y62" t="n">
         <v>6</v>
@@ -15272,10 +15272,10 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>5218</v>
+        <v>5334</v>
       </c>
       <c r="X64" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="Y64" t="n">
         <v>26</v>
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
       <c r="W65" t="n">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="X65" t="n">
-        <v>7.93</v>
+        <v>7.61</v>
       </c>
       <c r="Y65" t="n">
         <v>118</v>
@@ -15729,13 +15729,13 @@
         </is>
       </c>
       <c r="V66" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="W66" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="X66" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="Y66" t="n">
         <v>19</v>
@@ -15964,7 +15964,7 @@
         <v>0.011</v>
       </c>
       <c r="W67" t="n">
-        <v>3962</v>
+        <v>4006</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="n">
@@ -16194,7 +16194,7 @@
         <v>0.074</v>
       </c>
       <c r="W68" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="X68" t="n">
         <v>13.5</v>
@@ -16423,13 +16423,13 @@
         </is>
       </c>
       <c r="V69" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="W69" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="X69" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="Y69" t="n">
         <v>24</v>
@@ -16658,10 +16658,10 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>3531</v>
+        <v>3520</v>
       </c>
       <c r="X70" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="Y70" t="n">
         <v>5</v>
@@ -16890,10 +16890,10 @@
         <v>0.035</v>
       </c>
       <c r="W71" t="n">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="X71" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Y71" t="n">
         <v>11</v>
@@ -17122,10 +17122,10 @@
         <v>0.003</v>
       </c>
       <c r="W72" t="n">
-        <v>12669</v>
+        <v>12885</v>
       </c>
       <c r="X72" t="n">
-        <v>40.4</v>
+        <v>41.1</v>
       </c>
       <c r="Y72" t="n">
         <v>31</v>
@@ -17354,10 +17354,10 @@
         <v>0.031</v>
       </c>
       <c r="W73" t="n">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="X73" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="Y73" t="n">
         <v>27</v>
@@ -17586,7 +17586,7 @@
         <v>0.052</v>
       </c>
       <c r="W74" t="n">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="n">
@@ -17816,10 +17816,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>3819</v>
+        <v>3828</v>
       </c>
       <c r="X75" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="Y75" t="n">
         <v>42</v>
@@ -18048,10 +18048,10 @@
         <v>0.006</v>
       </c>
       <c r="W76" t="n">
-        <v>4884</v>
+        <v>4857</v>
       </c>
       <c r="X76" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y76" t="n">
         <v>23</v>
@@ -18276,10 +18276,10 @@
         <v>0.025</v>
       </c>
       <c r="W77" t="n">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="X77" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
@@ -18496,10 +18496,10 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>31015</v>
+        <v>31208</v>
       </c>
       <c r="X78" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y78" t="n">
         <v>62</v>
@@ -18728,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>105242</v>
+        <v>105181</v>
       </c>
       <c r="X79" t="n">
         <v>30.3</v>
@@ -18957,10 +18957,10 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.36</v>
+        <v>0.353</v>
       </c>
       <c r="W80" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="n">
@@ -19187,13 +19187,13 @@
         </is>
       </c>
       <c r="V81" t="n">
-        <v>0.235</v>
+        <v>0.232</v>
       </c>
       <c r="W81" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="X81" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Y81" t="n">
         <v>21</v>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W82" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="n">
@@ -21329,31 +21329,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24.27</v>
+        <v>447.2</v>
       </c>
       <c r="D50" t="n">
-        <v>27.53</v>
+        <v>349.57</v>
       </c>
       <c r="E50" t="n">
-        <v>-11.8</v>
+        <v>27.9</v>
       </c>
       <c r="F50" t="n">
-        <v>61.81</v>
+        <v>70.55</v>
       </c>
       <c r="G50" t="n">
-        <v>0.65</v>
+        <v>31.6</v>
       </c>
       <c r="H50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -21364,140 +21364,140 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>447.2</v>
+        <v>12.44</v>
       </c>
       <c r="D51" t="n">
-        <v>349.57</v>
+        <v>12.86</v>
       </c>
       <c r="E51" t="n">
-        <v>27.9</v>
+        <v>-3.3</v>
       </c>
       <c r="F51" t="n">
-        <v>70.55</v>
+        <v>69.12</v>
       </c>
       <c r="G51" t="n">
-        <v>31.6</v>
+        <v>2.35</v>
       </c>
       <c r="H51" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>12.44</v>
+        <v>424.45</v>
       </c>
       <c r="D52" t="n">
-        <v>12.86</v>
+        <v>473.17</v>
       </c>
       <c r="E52" t="n">
-        <v>-3.3</v>
+        <v>-10.3</v>
       </c>
       <c r="F52" t="n">
-        <v>69.12</v>
+        <v>56.22</v>
       </c>
       <c r="G52" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="H52" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>424.45</v>
+        <v>3.26</v>
       </c>
       <c r="D53" t="n">
-        <v>473.17</v>
+        <v>2.82</v>
       </c>
       <c r="E53" t="n">
-        <v>-10.3</v>
+        <v>15.6</v>
       </c>
       <c r="F53" t="n">
-        <v>56.22</v>
+        <v>64.45</v>
       </c>
       <c r="G53" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3.26</v>
+        <v>24.27</v>
       </c>
       <c r="D54" t="n">
-        <v>2.82</v>
+        <v>27.53</v>
       </c>
       <c r="E54" t="n">
-        <v>15.6</v>
+        <v>-11.8</v>
       </c>
       <c r="F54" t="n">
-        <v>64.45</v>
+        <v>61.81</v>
       </c>
       <c r="G54" t="n">
-        <v>2.02</v>
+        <v>0.65</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-14/enriched_analysis.xlsx
+++ b/output/2026-10-14/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.241</v>
+        <v>2.207</v>
       </c>
       <c r="W2" t="n">
-        <v>2811</v>
+        <v>2855</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.829</v>
+        <v>0.834</v>
       </c>
       <c r="W3" t="n">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="X3" t="n">
         <v>136</v>
@@ -1396,10 +1396,10 @@
         <v>0.021</v>
       </c>
       <c r="W4" t="n">
-        <v>3433</v>
+        <v>3490</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="Y4" t="n">
         <v>18</v>
@@ -1628,7 +1628,7 @@
         <v>0.044</v>
       </c>
       <c r="W5" t="n">
-        <v>3031</v>
+        <v>3034</v>
       </c>
       <c r="X5" t="n">
         <v>10.4</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.047</v>
+        <v>1.044</v>
       </c>
       <c r="W6" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="X6" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="Y6" t="n">
         <v>111</v>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.513</v>
+        <v>0.516</v>
       </c>
       <c r="W7" t="n">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="X7" t="n">
         <v>14.1</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.203</v>
+        <v>1.223</v>
       </c>
       <c r="W8" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="X8" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Y8" t="n">
         <v>22</v>
@@ -2556,10 +2556,10 @@
         <v>0.322</v>
       </c>
       <c r="W9" t="n">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="X9" t="n">
-        <v>9.32</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Y9" t="n">
         <v>7</v>
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1.194</v>
+        <v>1.246</v>
       </c>
       <c r="W10" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="X10" t="n">
-        <v>7.14</v>
+        <v>6.85</v>
       </c>
       <c r="Y10" t="n">
         <v>17</v>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.443</v>
+        <v>1.471</v>
       </c>
       <c r="W11" t="n">
-        <v>9377</v>
+        <v>9200</v>
       </c>
       <c r="X11" t="n">
-        <v>1579</v>
+        <v>1549</v>
       </c>
       <c r="Y11" t="n">
         <v>-53</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
       <c r="W12" t="n">
-        <v>15249</v>
+        <v>15142</v>
       </c>
       <c r="X12" t="n">
-        <v>38.8</v>
+        <v>38.5</v>
       </c>
       <c r="Y12" t="n">
         <v>83</v>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2.356</v>
+        <v>2.357</v>
       </c>
       <c r="W13" t="n">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="X13" t="n">
         <v>195</v>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.127</v>
+        <v>0.124</v>
       </c>
       <c r="W14" t="n">
-        <v>686</v>
+        <v>704</v>
       </c>
       <c r="X14" t="n">
-        <v>25.9</v>
+        <v>26.6</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3945,13 +3945,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1673</v>
+        <v>1644</v>
       </c>
       <c r="X15" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="Y15" t="n">
         <v>55</v>
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
       <c r="W16" t="n">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="X16" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
         <v>19</v>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1.959</v>
+        <v>1.922</v>
       </c>
       <c r="W17" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
@@ -4640,10 +4640,10 @@
         <v>0.174</v>
       </c>
       <c r="W18" t="n">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="X18" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="Y18" t="n">
         <v>2</v>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.233</v>
+        <v>0.237</v>
       </c>
       <c r="W19" t="n">
-        <v>1476</v>
+        <v>1453</v>
       </c>
       <c r="X19" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="Y19" t="n">
         <v>8</v>
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="W20" t="n">
-        <v>2494</v>
+        <v>2502</v>
       </c>
       <c r="X20" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Y20" t="n">
         <v>-3</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>2542</v>
+        <v>2547</v>
       </c>
       <c r="X21" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>3.144</v>
+        <v>3.154</v>
       </c>
       <c r="W22" t="n">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="X22" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="Y22" t="n">
         <v>30</v>
@@ -5789,13 +5789,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.178</v>
+        <v>0.167</v>
       </c>
       <c r="W23" t="n">
-        <v>621</v>
+        <v>663</v>
       </c>
       <c r="X23" t="n">
-        <v>51.9</v>
+        <v>55.3</v>
       </c>
       <c r="Y23" t="n">
         <v>3</v>
@@ -5949,16 +5949,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>AEROENTER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>AEROFLEX ENTERPRISES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5966,40 +5966,40 @@
         </is>
       </c>
       <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
         <v>5</v>
       </c>
-      <c r="F24" t="n">
-        <v>22</v>
-      </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I24" t="n">
-        <v>88.95999999999999</v>
+        <v>134.61</v>
       </c>
       <c r="J24" t="n">
-        <v>68.68000000000001</v>
+        <v>120.25</v>
       </c>
       <c r="K24" t="n">
-        <v>29.5</v>
+        <v>11.9</v>
       </c>
       <c r="L24" t="n">
-        <v>71.36</v>
+        <v>51.59</v>
       </c>
       <c r="M24" t="n">
-        <v>0.86</v>
+        <v>2.11</v>
       </c>
       <c r="N24" t="n">
-        <v>8585000</v>
+        <v>21127925</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>8585000</v>
+        <v>21127925</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -6017,50 +6017,56 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.101</v>
+        <v>0.136</v>
       </c>
       <c r="W24" t="n">
-        <v>848</v>
+        <v>1548</v>
       </c>
       <c r="X24" t="n">
-        <v>36.9</v>
+        <v>15.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.44</v>
+        <v>-23</v>
       </c>
       <c r="AA24" t="n">
-        <v>39</v>
+        <v>955</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.55</v>
+        <v>8.07</v>
       </c>
       <c r="AC24" t="n">
-        <v>23.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
+        <v>-831</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>131.75</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>103.83</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>59</v>
+      </c>
       <c r="AJ24" t="n">
-        <v>68.68000000000001</v>
+        <v>120.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>29.5</v>
+        <v>11.9</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -6074,27 +6080,27 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AT24" t="n">
         <v>0</v>
@@ -6118,13 +6124,13 @@
         <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>8585000</v>
+        <v>21127925</v>
       </c>
       <c r="BB24" t="n">
-        <v>8585000</v>
+        <v>21127925</v>
       </c>
       <c r="BC24" t="n">
-        <v>8585000</v>
+        <v>21127925</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -6160,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>8585000</v>
+        <v>21127925</v>
       </c>
       <c r="BP24" t="n">
         <v>1</v>
@@ -6175,12 +6181,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AEROENTER</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AEROFLEX ENTERPRISES LIMITED</t>
+          <t>INDOCO REMEDIES LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6192,111 +6198,111 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H25" t="n">
         <v>-1</v>
       </c>
       <c r="I25" t="n">
-        <v>134.61</v>
+        <v>226.55</v>
       </c>
       <c r="J25" t="n">
-        <v>120.25</v>
+        <v>239.13</v>
       </c>
       <c r="K25" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>12657065</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>12657065</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>8</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>09-09-2026</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2132</v>
+      </c>
+      <c r="X25" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>141</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>239.82</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>222.54</v>
+      </c>
+      <c r="AI25" t="n">
         <v>11.9</v>
       </c>
-      <c r="L25" t="n">
-        <v>51.59</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="N25" t="n">
-        <v>21127925</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>21127925</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S25" t="b">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1568</v>
-      </c>
-      <c r="X25" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>152</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>955</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>-831</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>131.75</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>103.83</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>59</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>120.25</v>
+        <v>239.1283771018326</v>
       </c>
       <c r="AK25" t="n">
-        <v>11.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -6311,22 +6317,22 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AS25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
@@ -6335,13 +6341,13 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -6350,13 +6356,13 @@
         <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>21127925</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>21127925</v>
+        <v>12657065</v>
       </c>
       <c r="BC25" t="n">
-        <v>21127925</v>
+        <v>12657065</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -6392,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>21127925</v>
+        <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BQ25" t="n">
         <v>0</v>
@@ -6407,16 +6413,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INDOCO REMEDIES LIMITED</t>
+          <t>CONTROL PRINT LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6424,141 +6430,141 @@
         </is>
       </c>
       <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>587.75</v>
+      </c>
+      <c r="J26" t="n">
+        <v>581.41</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N26" t="n">
+        <v>32335370</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>32335370</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>15</v>
-      </c>
-      <c r="G26" t="n">
-        <v>13</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>226.55</v>
-      </c>
-      <c r="J26" t="n">
-        <v>239.13</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="L26" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="N26" t="n">
-        <v>12657065</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>12657065</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S26" t="b">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>8</v>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.06</v>
+        <v>0.343</v>
       </c>
       <c r="W26" t="n">
-        <v>2112</v>
+        <v>944</v>
       </c>
       <c r="X26" t="n">
-        <v>98.09999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="Y26" t="n">
         <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>141</v>
+        <v>-41</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.92</v>
+        <v>7.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.33</v>
+        <v>22.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="n">
-        <v>239.82</v>
+        <v>591.13</v>
       </c>
       <c r="AH26" t="n">
-        <v>222.54</v>
+        <v>628.83</v>
       </c>
       <c r="AI26" t="n">
-        <v>11.9</v>
+        <v>-9.6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>239.1283771018326</v>
+        <v>581.4145464353143</v>
       </c>
       <c r="AK26" t="n">
-        <v>-5.3</v>
+        <v>1.1</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AR26" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AS26" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="AT26" t="n">
         <v>0</v>
@@ -6567,13 +6573,13 @@
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -6582,13 +6588,13 @@
         <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>32335370</v>
       </c>
       <c r="BB26" t="n">
-        <v>12657065</v>
+        <v>32335370</v>
       </c>
       <c r="BC26" t="n">
-        <v>12657065</v>
+        <v>32335370</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6624,10 +6630,10 @@
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>32335370</v>
       </c>
       <c r="BP26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BQ26" t="n">
         <v>0</v>
@@ -6639,12 +6645,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>AURUM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CONTROL PRINT LIMITED</t>
+          <t>Aurum PropTech Limited</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -6656,40 +6662,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I27" t="n">
-        <v>587.75</v>
+        <v>236.43</v>
       </c>
       <c r="J27" t="n">
-        <v>581.41</v>
+        <v>223.86</v>
       </c>
       <c r="K27" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="L27" t="n">
-        <v>52.68</v>
+        <v>50.34</v>
       </c>
       <c r="M27" t="n">
-        <v>3.23</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>32335370</v>
+        <v>11192763</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>32335370</v>
+        <v>11192763</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -6703,124 +6709,124 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.337</v>
+        <v>0.064</v>
       </c>
       <c r="W27" t="n">
-        <v>959</v>
+        <v>1747</v>
       </c>
       <c r="X27" t="n">
-        <v>13.4</v>
+        <v>271</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>-48</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>-3</v>
       </c>
       <c r="AA27" t="n">
-        <v>-41</v>
+        <v>2250</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.75</v>
+        <v>6.59</v>
       </c>
       <c r="AC27" t="n">
-        <v>22.6</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
         <v>0.01</v>
       </c>
       <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-5760</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>225.72</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>197.6</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>223.85526</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
         <v>1</v>
       </c>
-      <c r="AF27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>591.13</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>628.83</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>581.4145464353143</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
       <c r="AV27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>4539847</v>
       </c>
       <c r="BA27" t="n">
-        <v>32335370</v>
+        <v>11192763</v>
       </c>
       <c r="BB27" t="n">
-        <v>32335370</v>
+        <v>11192763</v>
       </c>
       <c r="BC27" t="n">
-        <v>32335370</v>
+        <v>11192763</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
@@ -6856,10 +6862,10 @@
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>32335370</v>
+        <v>11192763</v>
       </c>
       <c r="BP27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ27" t="n">
         <v>0</v>
@@ -6871,12 +6877,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AURUM</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aurum PropTech Limited</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -6891,37 +6897,37 @@
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>-2</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>236.43</v>
+        <v>125.32</v>
       </c>
       <c r="J28" t="n">
-        <v>223.86</v>
+        <v>171.54</v>
       </c>
       <c r="K28" t="n">
-        <v>5.6</v>
+        <v>-26.9</v>
       </c>
       <c r="L28" t="n">
-        <v>50.34</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>11192763</v>
+        <v>11081344</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>11192763</v>
+        <v>11081344</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -6935,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -6943,52 +6949,52 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="W28" t="n">
-        <v>1745</v>
+        <v>1690</v>
       </c>
       <c r="X28" t="n">
-        <v>270</v>
+        <v>38.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>-48</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="n">
-        <v>-3</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>2250</v>
+        <v>83</v>
       </c>
       <c r="AB28" t="n">
-        <v>6.59</v>
+        <v>0.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>30.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>-5760</v>
+        <v>23</v>
       </c>
       <c r="AG28" t="n">
-        <v>225.72</v>
+        <v>167.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>197.6</v>
+        <v>460.07</v>
       </c>
       <c r="AI28" t="n">
-        <v>37.8</v>
+        <v>-1.8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>223.85526</v>
+        <v>171.5378328173375</v>
       </c>
       <c r="AK28" t="n">
-        <v>5.6</v>
+        <v>-26.9</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -7007,7 +7013,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
@@ -7016,10 +7022,10 @@
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AR28" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AS28" t="n">
         <v>14</v>
@@ -7031,28 +7037,28 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4539847</v>
+        <v>83720</v>
       </c>
       <c r="BA28" t="n">
-        <v>11192763</v>
+        <v>83720</v>
       </c>
       <c r="BB28" t="n">
-        <v>11192763</v>
+        <v>11081344</v>
       </c>
       <c r="BC28" t="n">
-        <v>11192763</v>
+        <v>11081344</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -7088,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>11192763</v>
+        <v>83720</v>
       </c>
       <c r="BP28" t="n">
         <v>1</v>
@@ -7103,12 +7109,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7123,37 +7129,37 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>125.32</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>171.54</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-26.9</v>
+        <v>29.5</v>
       </c>
       <c r="L29" t="n">
-        <v>74.51000000000001</v>
+        <v>71.36</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="N29" t="n">
-        <v>11081344</v>
+        <v>8585000</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>11081344</v>
+        <v>8585000</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -7167,60 +7173,54 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.068</v>
+        <v>0.097</v>
       </c>
       <c r="W29" t="n">
-        <v>1628</v>
+        <v>882</v>
       </c>
       <c r="X29" t="n">
-        <v>37.4</v>
+        <v>38.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>8.44</v>
       </c>
       <c r="AA29" t="n">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="AC29" t="n">
-        <v>30.3</v>
+        <v>23.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AE29" t="b">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>167.31</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>460.07</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>-1.8</v>
-      </c>
+        <v>19.61</v>
+      </c>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="n">
-        <v>171.5378328173375</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AK29" t="n">
-        <v>-26.9</v>
+        <v>29.5</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -7229,62 +7229,62 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
         <v>1</v>
       </c>
       <c r="AW29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AX29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>83720</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>83720</v>
+        <v>8585000</v>
       </c>
       <c r="BB29" t="n">
-        <v>11081344</v>
+        <v>8585000</v>
       </c>
       <c r="BC29" t="n">
-        <v>11081344</v>
+        <v>8585000</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -7320,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>83720</v>
+        <v>8585000</v>
       </c>
       <c r="BP29" t="n">
         <v>1</v>
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="W30" t="n">
-        <v>59791</v>
+        <v>59882</v>
       </c>
       <c r="X30" t="n">
         <v>22.4</v>
@@ -7639,13 +7639,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.54</v>
+        <v>0.536</v>
       </c>
       <c r="W31" t="n">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="X31" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="Y31" t="n">
         <v>13</v>
@@ -7874,10 +7874,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>55776</v>
+        <v>55414</v>
       </c>
       <c r="X32" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="Y32" t="n">
         <v>5</v>
@@ -8106,10 +8106,10 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="X33" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="Y33" t="n">
         <v>-5</v>
@@ -8335,13 +8335,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>1.597</v>
+        <v>1.633</v>
       </c>
       <c r="W34" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="X34" t="n">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="Y34" t="n">
         <v>-14</v>
@@ -8567,13 +8567,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.153</v>
+        <v>0.162</v>
       </c>
       <c r="W35" t="n">
-        <v>4189</v>
+        <v>3939</v>
       </c>
       <c r="X35" t="n">
-        <v>7.9</v>
+        <v>7.41</v>
       </c>
       <c r="Y35" t="n">
         <v>2</v>
@@ -9027,13 +9027,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.26</v>
+        <v>0.261</v>
       </c>
       <c r="W37" t="n">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="X37" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="Y37" t="n">
         <v>9</v>
@@ -9261,7 +9261,7 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
-        <v>5.58</v>
+        <v>5.76</v>
       </c>
       <c r="Y38" t="n">
         <v>-68</v>
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>1.082</v>
+        <v>1.092</v>
       </c>
       <c r="W39" t="n">
-        <v>1838</v>
+        <v>1820</v>
       </c>
       <c r="X39" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Y39" t="n">
         <v>12</v>
@@ -9722,10 +9722,10 @@
         <v>0.01</v>
       </c>
       <c r="W40" t="n">
-        <v>15097</v>
+        <v>14910</v>
       </c>
       <c r="X40" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="Y40" t="n">
         <v>28</v>
@@ -9951,13 +9951,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.325</v>
+        <v>0.328</v>
       </c>
       <c r="W41" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="X41" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Y41" t="n">
         <v>12</v>
@@ -9975,7 +9975,7 @@
         <v>7.91</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
@@ -10186,10 +10186,10 @@
         <v>0.004</v>
       </c>
       <c r="W42" t="n">
-        <v>47866</v>
+        <v>48236</v>
       </c>
       <c r="X42" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Y42" t="n">
         <v>26</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="W43" t="n">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="X43" t="n">
-        <v>53.6</v>
+        <v>53.4</v>
       </c>
       <c r="Y43" t="n">
         <v>21</v>
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="W44" t="n">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="X44" t="n">
         <v>14.4</v>
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>1.845</v>
+        <v>1.876</v>
       </c>
       <c r="W45" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="n">
@@ -11109,13 +11109,13 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.52</v>
+        <v>0.514</v>
       </c>
       <c r="W46" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="X46" t="n">
-        <v>35.6</v>
+        <v>36</v>
       </c>
       <c r="Y46" t="n">
         <v>21</v>
@@ -11731,188 +11731,188 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
         <v>8</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>25</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I49" t="n">
+        <v>447.2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="K49" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="L49" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="M49" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N49" t="n">
+        <v>315995536</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>315995536</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
         <v>11</v>
       </c>
-      <c r="F49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>168.14</v>
-      </c>
-      <c r="J49" t="n">
-        <v>174.27</v>
-      </c>
-      <c r="K49" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="L49" t="n">
-        <v>61.48</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N49" t="n">
-        <v>10743104</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>10743104</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S49" t="b">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>7</v>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.509</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="W49" t="n">
-        <v>211</v>
+        <v>3861</v>
       </c>
       <c r="X49" t="n">
-        <v>36.6</v>
+        <v>27</v>
       </c>
       <c r="Y49" t="n">
-        <v>-44</v>
+        <v>2</v>
       </c>
       <c r="Z49" t="n">
-        <v>-3.28</v>
+        <v>127</v>
       </c>
       <c r="AA49" t="n">
-        <v>141</v>
+        <v>-14</v>
       </c>
       <c r="AB49" t="n">
-        <v>-4.05</v>
+        <v>6.41</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.67</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.44</v>
+        <v>1.05</v>
       </c>
       <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>443.07</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>433.75</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>349.5746258337085</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ49" t="n">
+        <v>56</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
         <v>1</v>
       </c>
-      <c r="AF49" t="n">
-        <v>-35.96</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>169.97</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>176.62</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>174.2652478588113</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ49" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0</v>
-      </c>
       <c r="AV49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX49" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="BA49" t="n">
-        <v>10743104</v>
+        <v>213764633</v>
       </c>
       <c r="BB49" t="n">
-        <v>10743104</v>
+        <v>213764633</v>
       </c>
       <c r="BC49" t="n">
-        <v>10743104</v>
+        <v>315995536</v>
       </c>
       <c r="BD49" t="n">
         <v>0</v>
@@ -11948,7 +11948,7 @@
         <v>0</v>
       </c>
       <c r="BO49" t="n">
-        <v>10743104</v>
+        <v>213764633</v>
       </c>
       <c r="BP49" t="n">
         <v>1</v>
@@ -11963,12 +11963,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -11980,107 +11980,103 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F50" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="J50" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="L50" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N50" t="n">
+        <v>23479616</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>23479616</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
         <v>25</v>
       </c>
-      <c r="H50" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I50" t="n">
-        <v>447.2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>349.57</v>
-      </c>
-      <c r="K50" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="L50" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="M50" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="N50" t="n">
-        <v>315995536</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>315995536</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S50" t="b">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>11</v>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.649</v>
       </c>
       <c r="W50" t="n">
-        <v>3907</v>
+        <v>362</v>
       </c>
       <c r="X50" t="n">
-        <v>27.3</v>
+        <v>1166</v>
       </c>
       <c r="Y50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>127</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="n">
-        <v>-14</v>
+        <v>-98</v>
       </c>
       <c r="AB50" t="n">
-        <v>6.41</v>
+        <v>0.01</v>
       </c>
       <c r="AC50" t="n">
-        <v>9.890000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="n">
-        <v>443.07</v>
+        <v>12.83</v>
       </c>
       <c r="AH50" t="n">
-        <v>433.75</v>
+        <v>12.91</v>
       </c>
       <c r="AI50" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="AJ50" t="n">
-        <v>349.5746258337085</v>
+        <v>12.85608234597773</v>
       </c>
       <c r="AK50" t="n">
-        <v>27.9</v>
+        <v>-3.2</v>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
@@ -12094,57 +12090,57 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ50" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AR50" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AS50" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
       <c r="AU50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW50" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AX50" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>213764633</v>
+        <v>2496337</v>
       </c>
       <c r="BB50" t="n">
-        <v>213764633</v>
+        <v>16559572</v>
       </c>
       <c r="BC50" t="n">
-        <v>315995536</v>
+        <v>23479616</v>
       </c>
       <c r="BD50" t="n">
         <v>0</v>
@@ -12180,7 +12176,7 @@
         <v>0</v>
       </c>
       <c r="BO50" t="n">
-        <v>213764633</v>
+        <v>2496337</v>
       </c>
       <c r="BP50" t="n">
         <v>1</v>
@@ -12195,12 +12191,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -12212,40 +12208,40 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>12.44</v>
+        <v>424.45</v>
       </c>
       <c r="J51" t="n">
-        <v>12.86</v>
+        <v>473.17</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.3</v>
+        <v>-10.3</v>
       </c>
       <c r="L51" t="n">
-        <v>69.12</v>
+        <v>56.22</v>
       </c>
       <c r="M51" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="N51" t="n">
-        <v>23479616</v>
+        <v>23279819</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>23479616</v>
+        <v>23279819</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -12259,56 +12255,60 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>0.695</v>
+        <v>0.044</v>
       </c>
       <c r="W51" t="n">
-        <v>338</v>
+        <v>5256</v>
       </c>
       <c r="X51" t="n">
-        <v>1091</v>
+        <v>27.3</v>
       </c>
       <c r="Y51" t="n">
-        <v>-61</v>
-      </c>
-      <c r="Z51" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>59</v>
+      </c>
       <c r="AA51" t="n">
-        <v>-98</v>
+        <v>-52</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.01</v>
+        <v>3.48</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.46</v>
+        <v>24.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="AE51" t="b">
         <v>1</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
+      <c r="AF51" t="n">
+        <v>7</v>
+      </c>
       <c r="AG51" t="n">
-        <v>12.83</v>
+        <v>479.42</v>
       </c>
       <c r="AH51" t="n">
-        <v>12.91</v>
+        <v>548.23</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.6</v>
+        <v>-16.8</v>
       </c>
       <c r="AJ51" t="n">
-        <v>12.85608234597773</v>
+        <v>473.1670528455285</v>
       </c>
       <c r="AK51" t="n">
-        <v>-3.2</v>
+        <v>-10.3</v>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
@@ -12327,22 +12327,22 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AQ51" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="AR51" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AS51" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AT51" t="n">
         <v>0</v>
@@ -12351,13 +12351,13 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW51" t="n">
         <v>4</v>
       </c>
-      <c r="AW51" t="n">
-        <v>22</v>
-      </c>
       <c r="AX51" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AY51" t="n">
         <v>0</v>
@@ -12366,13 +12366,13 @@
         <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>2496337</v>
+        <v>11585069</v>
       </c>
       <c r="BB51" t="n">
-        <v>16559572</v>
+        <v>23279819</v>
       </c>
       <c r="BC51" t="n">
-        <v>23479616</v>
+        <v>23279819</v>
       </c>
       <c r="BD51" t="n">
         <v>0</v>
@@ -12408,10 +12408,10 @@
         <v>0</v>
       </c>
       <c r="BO51" t="n">
-        <v>2496337</v>
+        <v>11585069</v>
       </c>
       <c r="BP51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ51" t="n">
         <v>0</v>
@@ -12423,12 +12423,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -12440,40 +12440,40 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G52" t="n">
         <v>12</v>
       </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>424.45</v>
+        <v>3.26</v>
       </c>
       <c r="J52" t="n">
-        <v>473.17</v>
+        <v>2.82</v>
       </c>
       <c r="K52" t="n">
-        <v>-10.3</v>
+        <v>15.6</v>
       </c>
       <c r="L52" t="n">
-        <v>56.22</v>
+        <v>64.45</v>
       </c>
       <c r="M52" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="N52" t="n">
-        <v>23279819</v>
+        <v>20159573</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>23279819</v>
+        <v>20159573</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -12487,60 +12487,54 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="W52" t="n">
-        <v>5241</v>
-      </c>
-      <c r="X52" t="n">
-        <v>27.2</v>
-      </c>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
       <c r="Y52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="n">
-        <v>59</v>
+        <v>0.98</v>
       </c>
       <c r="AA52" t="n">
-        <v>-52</v>
+        <v>-86</v>
       </c>
       <c r="AB52" t="n">
-        <v>3.48</v>
+        <v>-0.03</v>
       </c>
       <c r="AC52" t="n">
-        <v>24.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.26</v>
+        <v>1.58</v>
       </c>
       <c r="AE52" t="b">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>7</v>
+        <v>14.22</v>
       </c>
       <c r="AG52" t="n">
-        <v>479.42</v>
+        <v>2.91</v>
       </c>
       <c r="AH52" t="n">
-        <v>548.23</v>
+        <v>3.16</v>
       </c>
       <c r="AI52" t="n">
-        <v>-16.8</v>
+        <v>-3.6</v>
       </c>
       <c r="AJ52" t="n">
-        <v>473.1670528455285</v>
+        <v>2.817550384346611</v>
       </c>
       <c r="AK52" t="n">
-        <v>-10.3</v>
+        <v>15.7</v>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
@@ -12549,32 +12543,32 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AS52" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AT52" t="n">
         <v>0</v>
@@ -12583,13 +12577,13 @@
         <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY52" t="n">
         <v>0</v>
@@ -12598,13 +12592,13 @@
         <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>11585069</v>
+        <v>20159573</v>
       </c>
       <c r="BB52" t="n">
-        <v>23279819</v>
+        <v>20159573</v>
       </c>
       <c r="BC52" t="n">
-        <v>23279819</v>
+        <v>20159573</v>
       </c>
       <c r="BD52" t="n">
         <v>0</v>
@@ -12640,10 +12634,10 @@
         <v>0</v>
       </c>
       <c r="BO52" t="n">
-        <v>11585069</v>
+        <v>20159573</v>
       </c>
       <c r="BP52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ52" t="n">
         <v>0</v>
@@ -12655,12 +12649,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -12672,40 +12666,40 @@
         </is>
       </c>
       <c r="E53" t="n">
+        <v>9</v>
+      </c>
+      <c r="F53" t="n">
         <v>3</v>
       </c>
-      <c r="F53" t="n">
-        <v>-2</v>
-      </c>
       <c r="G53" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I53" t="n">
-        <v>3.26</v>
+        <v>168.14</v>
       </c>
       <c r="J53" t="n">
-        <v>2.82</v>
+        <v>174.27</v>
       </c>
       <c r="K53" t="n">
-        <v>15.6</v>
+        <v>-3.5</v>
       </c>
       <c r="L53" t="n">
-        <v>64.45</v>
+        <v>61.48</v>
       </c>
       <c r="M53" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="N53" t="n">
-        <v>20159573</v>
+        <v>10743104</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>20159573</v>
+        <v>10743104</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -12719,54 +12713,60 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>24-09-2026</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
+      <c r="V53" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="W53" t="n">
+        <v>216</v>
+      </c>
+      <c r="X53" t="n">
+        <v>37.4</v>
+      </c>
       <c r="Y53" t="n">
-        <v>10</v>
+        <v>-44</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.98</v>
+        <v>-3.28</v>
       </c>
       <c r="AA53" t="n">
-        <v>-86</v>
+        <v>141</v>
       </c>
       <c r="AB53" t="n">
-        <v>-0.03</v>
+        <v>-4.05</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.27</v>
+        <v>8.67</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.58</v>
+        <v>0.44</v>
       </c>
       <c r="AE53" t="b">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>14.22</v>
+        <v>-35.96</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.91</v>
+        <v>169.97</v>
       </c>
       <c r="AH53" t="n">
-        <v>3.16</v>
+        <v>176.62</v>
       </c>
       <c r="AI53" t="n">
-        <v>-3.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.817550384346611</v>
+        <v>174.2652478588113</v>
       </c>
       <c r="AK53" t="n">
-        <v>15.7</v>
+        <v>-3.5</v>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
@@ -12775,29 +12775,29 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
           <t>24-09-2026</t>
         </is>
       </c>
-      <c r="AP53" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR53" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AS53" t="n">
         <v>20</v>
@@ -12809,13 +12809,13 @@
         <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AW53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AX53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AY53" t="n">
         <v>0</v>
@@ -12824,13 +12824,13 @@
         <v>0</v>
       </c>
       <c r="BA53" t="n">
-        <v>20159573</v>
+        <v>10743104</v>
       </c>
       <c r="BB53" t="n">
-        <v>20159573</v>
+        <v>10743104</v>
       </c>
       <c r="BC53" t="n">
-        <v>20159573</v>
+        <v>10743104</v>
       </c>
       <c r="BD53" t="n">
         <v>0</v>
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="BO53" t="n">
-        <v>20159573</v>
+        <v>10743104</v>
       </c>
       <c r="BP53" t="n">
         <v>1</v>
@@ -12953,13 +12953,13 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>0.241</v>
+        <v>0.234</v>
       </c>
       <c r="W54" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="X54" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="Y54" t="n">
         <v>16</v>
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="V55" t="n">
-        <v>0.229</v>
+        <v>0.228</v>
       </c>
       <c r="W55" t="n">
-        <v>1743</v>
+        <v>1748</v>
       </c>
       <c r="X55" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="Y55" t="n">
         <v>-3</v>
@@ -13420,10 +13420,10 @@
         <v>0.042</v>
       </c>
       <c r="W56" t="n">
-        <v>3224</v>
+        <v>3230</v>
       </c>
       <c r="X56" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Y56" t="n">
         <v>-4</v>
@@ -13649,13 +13649,13 @@
         </is>
       </c>
       <c r="V57" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="W57" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="X57" t="n">
-        <v>94.7</v>
+        <v>95</v>
       </c>
       <c r="Y57" t="n">
         <v>246</v>
@@ -13881,13 +13881,13 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="W58" t="n">
-        <v>7682</v>
+        <v>7511</v>
       </c>
       <c r="X58" t="n">
-        <v>30.8</v>
+        <v>30.1</v>
       </c>
       <c r="Y58" t="n">
         <v>25</v>
@@ -14341,13 +14341,13 @@
         </is>
       </c>
       <c r="V60" t="n">
-        <v>0.244</v>
+        <v>0.243</v>
       </c>
       <c r="W60" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="X60" t="n">
-        <v>53.6</v>
+        <v>53.8</v>
       </c>
       <c r="Y60" t="n">
         <v>-4</v>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>0.2</v>
+        <v>0.198</v>
       </c>
       <c r="W61" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="X61" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="Y61" t="n">
         <v>-1</v>
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="V62" t="n">
-        <v>0.474</v>
+        <v>0.479</v>
       </c>
       <c r="W62" t="n">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="X62" t="n">
-        <v>42.4</v>
+        <v>41.9</v>
       </c>
       <c r="Y62" t="n">
         <v>6</v>
@@ -15037,13 +15037,13 @@
         </is>
       </c>
       <c r="V63" t="n">
-        <v>0.29</v>
+        <v>0.291</v>
       </c>
       <c r="W63" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="X63" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y63" t="n">
         <v>-66</v>
@@ -15272,7 +15272,7 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>5334</v>
+        <v>5324</v>
       </c>
       <c r="X64" t="n">
         <v>12.5</v>
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="W65" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="X65" t="n">
-        <v>7.61</v>
+        <v>7.7</v>
       </c>
       <c r="Y65" t="n">
         <v>118</v>
@@ -15729,13 +15729,13 @@
         </is>
       </c>
       <c r="V66" t="n">
-        <v>0.143</v>
+        <v>0.145</v>
       </c>
       <c r="W66" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="X66" t="n">
-        <v>32.5</v>
+        <v>32.1</v>
       </c>
       <c r="Y66" t="n">
         <v>19</v>
@@ -15964,7 +15964,7 @@
         <v>0.011</v>
       </c>
       <c r="W67" t="n">
-        <v>4006</v>
+        <v>3927</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="n">
@@ -16191,13 +16191,13 @@
         </is>
       </c>
       <c r="V68" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="W68" t="n">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="X68" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y68" t="n">
         <v>-8</v>
@@ -16426,10 +16426,10 @@
         <v>0.097</v>
       </c>
       <c r="W69" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="X69" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="Y69" t="n">
         <v>24</v>
@@ -16658,10 +16658,10 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>3520</v>
+        <v>3454</v>
       </c>
       <c r="X70" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="Y70" t="n">
         <v>5</v>
@@ -16887,13 +16887,13 @@
         </is>
       </c>
       <c r="V71" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="W71" t="n">
-        <v>1399</v>
+        <v>1427</v>
       </c>
       <c r="X71" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="Y71" t="n">
         <v>11</v>
@@ -17122,10 +17122,10 @@
         <v>0.003</v>
       </c>
       <c r="W72" t="n">
-        <v>12885</v>
+        <v>12927</v>
       </c>
       <c r="X72" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="Y72" t="n">
         <v>31</v>
@@ -17351,13 +17351,13 @@
         </is>
       </c>
       <c r="V73" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="W73" t="n">
-        <v>960</v>
+        <v>989</v>
       </c>
       <c r="X73" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="Y73" t="n">
         <v>27</v>
@@ -17586,7 +17586,7 @@
         <v>0.052</v>
       </c>
       <c r="W74" t="n">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="n">
@@ -17816,10 +17816,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>3828</v>
+        <v>3817</v>
       </c>
       <c r="X75" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Y75" t="n">
         <v>42</v>
@@ -18048,7 +18048,7 @@
         <v>0.006</v>
       </c>
       <c r="W76" t="n">
-        <v>4857</v>
+        <v>4833</v>
       </c>
       <c r="X76" t="n">
         <v>12.5</v>
@@ -18276,10 +18276,10 @@
         <v>0.025</v>
       </c>
       <c r="W77" t="n">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="X77" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
@@ -18496,10 +18496,10 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>31208</v>
+        <v>30581</v>
       </c>
       <c r="X78" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y78" t="n">
         <v>62</v>
@@ -18728,10 +18728,10 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>105181</v>
+        <v>104630</v>
       </c>
       <c r="X79" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="Y79" t="n">
         <v>18</v>
@@ -18957,10 +18957,10 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="W80" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="n">
@@ -19187,13 +19187,13 @@
         </is>
       </c>
       <c r="V81" t="n">
-        <v>0.232</v>
+        <v>0.225</v>
       </c>
       <c r="W81" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="X81" t="n">
-        <v>22.9</v>
+        <v>23.7</v>
       </c>
       <c r="Y81" t="n">
         <v>21</v>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="W82" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="n">
@@ -20419,171 +20419,171 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>AEROENTER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>AEROFLEX ENTERPRISES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>88.95999999999999</v>
+        <v>134.61</v>
       </c>
       <c r="D24" t="n">
-        <v>68.68000000000001</v>
+        <v>120.25</v>
       </c>
       <c r="E24" t="n">
-        <v>29.5</v>
+        <v>11.9</v>
       </c>
       <c r="F24" t="n">
-        <v>71.36</v>
+        <v>51.59</v>
       </c>
       <c r="G24" t="n">
-        <v>0.86</v>
+        <v>2.11</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AEROENTER</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AEROFLEX ENTERPRISES LIMITED</t>
+          <t>INDOCO REMEDIES LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>134.61</v>
+        <v>226.55</v>
       </c>
       <c r="D25" t="n">
-        <v>120.25</v>
+        <v>239.13</v>
       </c>
       <c r="E25" t="n">
-        <v>11.9</v>
+        <v>-5.3</v>
       </c>
       <c r="F25" t="n">
-        <v>51.59</v>
+        <v>58.75</v>
       </c>
       <c r="G25" t="n">
-        <v>2.11</v>
+        <v>1.27</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INDOCO REMEDIES LIMITED</t>
+          <t>CONTROL PRINT LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>226.55</v>
+        <v>587.75</v>
       </c>
       <c r="D26" t="n">
-        <v>239.13</v>
+        <v>581.41</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.3</v>
+        <v>1.1</v>
       </c>
       <c r="F26" t="n">
-        <v>58.75</v>
+        <v>52.68</v>
       </c>
       <c r="G26" t="n">
-        <v>1.27</v>
+        <v>3.23</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>AURUM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CONTROL PRINT LIMITED</t>
+          <t>Aurum PropTech Limited</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>587.75</v>
+        <v>236.43</v>
       </c>
       <c r="D27" t="n">
-        <v>581.41</v>
+        <v>223.86</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="F27" t="n">
-        <v>52.68</v>
+        <v>50.34</v>
       </c>
       <c r="G27" t="n">
-        <v>3.23</v>
+        <v>1.12</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AURUM</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aurum PropTech Limited</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>236.43</v>
+        <v>125.32</v>
       </c>
       <c r="D28" t="n">
-        <v>223.86</v>
+        <v>171.54</v>
       </c>
       <c r="E28" t="n">
-        <v>5.6</v>
+        <v>-26.9</v>
       </c>
       <c r="F28" t="n">
-        <v>50.34</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -20594,35 +20594,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>125.32</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>171.54</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-26.9</v>
+        <v>29.5</v>
       </c>
       <c r="F29" t="n">
-        <v>74.51000000000001</v>
+        <v>71.36</v>
       </c>
       <c r="G29" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
@@ -21294,171 +21294,171 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>168.14</v>
+        <v>447.2</v>
       </c>
       <c r="D49" t="n">
-        <v>174.27</v>
+        <v>349.57</v>
       </c>
       <c r="E49" t="n">
-        <v>-3.5</v>
+        <v>27.9</v>
       </c>
       <c r="F49" t="n">
-        <v>61.48</v>
+        <v>70.55</v>
       </c>
       <c r="G49" t="n">
-        <v>1.07</v>
+        <v>31.6</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>447.2</v>
+        <v>12.44</v>
       </c>
       <c r="D50" t="n">
-        <v>349.57</v>
+        <v>12.86</v>
       </c>
       <c r="E50" t="n">
-        <v>27.9</v>
+        <v>-3.3</v>
       </c>
       <c r="F50" t="n">
-        <v>70.55</v>
+        <v>69.12</v>
       </c>
       <c r="G50" t="n">
-        <v>31.6</v>
+        <v>2.35</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12.44</v>
+        <v>424.45</v>
       </c>
       <c r="D51" t="n">
-        <v>12.86</v>
+        <v>473.17</v>
       </c>
       <c r="E51" t="n">
-        <v>-3.3</v>
+        <v>-10.3</v>
       </c>
       <c r="F51" t="n">
-        <v>69.12</v>
+        <v>56.22</v>
       </c>
       <c r="G51" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="H51" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SHAKTI PUMPS (INDIA) LIMITED</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>424.45</v>
+        <v>3.26</v>
       </c>
       <c r="D52" t="n">
-        <v>473.17</v>
+        <v>2.82</v>
       </c>
       <c r="E52" t="n">
-        <v>-10.3</v>
+        <v>15.6</v>
       </c>
       <c r="F52" t="n">
-        <v>56.22</v>
+        <v>64.45</v>
       </c>
       <c r="G52" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="H52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3.26</v>
+        <v>168.14</v>
       </c>
       <c r="D53" t="n">
-        <v>2.82</v>
+        <v>174.27</v>
       </c>
       <c r="E53" t="n">
-        <v>15.6</v>
+        <v>-3.5</v>
       </c>
       <c r="F53" t="n">
-        <v>64.45</v>
+        <v>61.48</v>
       </c>
       <c r="G53" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>

--- a/output/2026-10-14/enriched_analysis.xlsx
+++ b/output/2026-10-14/enriched_analysis.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.216</v>
+        <v>2.212</v>
       </c>
       <c r="W2" t="n">
-        <v>2843</v>
+        <v>2848</v>
       </c>
       <c r="X2" t="n">
         <v>22.3</v>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mayur Uniquoters Ltd</t>
+          <t>MAYUR UNIQUOTERS LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1396,7 +1396,7 @@
         <v>0.021</v>
       </c>
       <c r="W4" t="n">
-        <v>3491</v>
+        <v>3485</v>
       </c>
       <c r="X4" t="n">
         <v>15.8</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="W5" t="n">
-        <v>3053</v>
+        <v>3042</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.044</v>
+        <v>1.039</v>
       </c>
       <c r="W6" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="X6" t="n">
-        <v>86.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y6" t="n">
         <v>111</v>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.237</v>
+        <v>0.238</v>
       </c>
       <c r="W8" t="n">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="X8" t="n">
         <v>24.6</v>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.126</v>
+        <v>0.122</v>
       </c>
       <c r="W9" t="n">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="X9" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.513</v>
+        <v>0.51</v>
       </c>
       <c r="W10" t="n">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="X10" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="Y10" t="n">
         <v>19</v>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.219</v>
+        <v>1.227</v>
       </c>
       <c r="W11" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="X11" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Y11" t="n">
         <v>22</v>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>1.246</v>
+        <v>1.202</v>
       </c>
       <c r="W13" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="X13" t="n">
-        <v>6.86</v>
+        <v>7.11</v>
       </c>
       <c r="Y13" t="n">
         <v>17</v>
@@ -3712,7 +3712,7 @@
         <v>0.048</v>
       </c>
       <c r="W14" t="n">
-        <v>15105</v>
+        <v>15124</v>
       </c>
       <c r="X14" t="n">
         <v>38.5</v>
@@ -4176,7 +4176,7 @@
         <v>0.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="X16" t="n">
         <v>22.1</v>
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="W17" t="n">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="X17" t="n">
-        <v>39.4</v>
+        <v>39.6</v>
       </c>
       <c r="Y17" t="n">
         <v>2</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.472</v>
       </c>
       <c r="W18" t="n">
-        <v>9142</v>
+        <v>9191</v>
       </c>
       <c r="X18" t="n">
-        <v>1539</v>
+        <v>1547</v>
       </c>
       <c r="Y18" t="n">
         <v>-53</v>
@@ -4872,10 +4872,10 @@
         <v>0.125</v>
       </c>
       <c r="W19" t="n">
-        <v>2504</v>
+        <v>2512</v>
       </c>
       <c r="X19" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>-3</v>
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="W20" t="n">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="X20" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="Y20" t="n">
         <v>19</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="X21" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
@@ -5566,10 +5566,10 @@
         <v>0.066</v>
       </c>
       <c r="W22" t="n">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="X22" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="Y22" t="n">
         <v>20</v>
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.338</v>
+        <v>0.336</v>
       </c>
       <c r="W23" t="n">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="X23" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="Y23" t="n">
         <v>13</v>
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>1.756</v>
+        <v>1.77</v>
       </c>
       <c r="W24" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
@@ -6257,13 +6257,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>3.138</v>
+        <v>3.149</v>
       </c>
       <c r="W25" t="n">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="X25" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="Y25" t="n">
         <v>30</v>
@@ -6483,13 +6483,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.173</v>
+        <v>0.171</v>
       </c>
       <c r="W26" t="n">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="X26" t="n">
-        <v>53.6</v>
+        <v>54.1</v>
       </c>
       <c r="Y26" t="n">
         <v>3</v>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.139</v>
+        <v>0.138</v>
       </c>
       <c r="W27" t="n">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="X27" t="n">
         <v>15.2</v>
@@ -6950,10 +6950,10 @@
         <v>0.059</v>
       </c>
       <c r="W28" t="n">
-        <v>2149</v>
+        <v>2162</v>
       </c>
       <c r="X28" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="Y28" t="n">
         <v>13</v>
@@ -7182,7 +7182,7 @@
         <v>0.064</v>
       </c>
       <c r="W29" t="n">
-        <v>1751</v>
+        <v>1745</v>
       </c>
       <c r="X29" t="n">
         <v>271</v>
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="W30" t="n">
-        <v>58727</v>
+        <v>58909</v>
       </c>
       <c r="X30" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Y30" t="n">
         <v>5</v>
@@ -7878,10 +7878,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>55583</v>
+        <v>55467</v>
       </c>
       <c r="X32" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="Y32" t="n">
         <v>5</v>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="X33" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="Y33" t="n">
         <v>-5</v>
@@ -8339,13 +8339,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="W34" t="n">
-        <v>3773</v>
+        <v>3782</v>
       </c>
       <c r="X34" t="n">
-        <v>7.11</v>
+        <v>7.13</v>
       </c>
       <c r="Y34" t="n">
         <v>2</v>
@@ -8574,10 +8574,10 @@
         <v>0.098</v>
       </c>
       <c r="W35" t="n">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="X35" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="Y35" t="n">
         <v>17</v>
@@ -8797,13 +8797,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
       <c r="W36" t="n">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="X36" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="Y36" t="n">
         <v>-1</v>
@@ -9035,7 +9035,7 @@
         <v>175</v>
       </c>
       <c r="X37" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="Y37" t="n">
         <v>31</v>
@@ -9257,13 +9257,13 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>0.264</v>
+        <v>0.262</v>
       </c>
       <c r="W38" t="n">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="X38" t="n">
-        <v>26.8</v>
+        <v>27.1</v>
       </c>
       <c r="Y38" t="n">
         <v>9</v>
@@ -9491,7 +9491,7 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
-        <v>5.59</v>
+        <v>5.58</v>
       </c>
       <c r="Y39" t="n">
         <v>-68</v>
@@ -9717,13 +9717,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>1.092</v>
+        <v>1.097</v>
       </c>
       <c r="W40" t="n">
-        <v>1820</v>
+        <v>1813</v>
       </c>
       <c r="X40" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Y40" t="n">
         <v>12</v>
@@ -9952,7 +9952,7 @@
         <v>0.01</v>
       </c>
       <c r="W41" t="n">
-        <v>14998</v>
+        <v>14989</v>
       </c>
       <c r="X41" t="n">
         <v>13.8</v>
@@ -10416,10 +10416,10 @@
         <v>0.004</v>
       </c>
       <c r="W43" t="n">
-        <v>47645</v>
+        <v>47535</v>
       </c>
       <c r="X43" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Y43" t="n">
         <v>26</v>
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
       <c r="W44" t="n">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="X44" t="n">
-        <v>53.9</v>
+        <v>54.3</v>
       </c>
       <c r="Y44" t="n">
         <v>21</v>
@@ -10669,7 +10669,7 @@
         <v>1.58</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
@@ -10877,13 +10877,13 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>1.643</v>
+        <v>1.691</v>
       </c>
       <c r="W45" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="X45" t="n">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="Y45" t="n">
         <v>-14</v>
@@ -11339,13 +11339,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.514</v>
+        <v>0.518</v>
       </c>
       <c r="W47" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="X47" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
       <c r="Y47" t="n">
         <v>21</v>
@@ -11574,10 +11574,10 @@
         <v>0.043</v>
       </c>
       <c r="W48" t="n">
-        <v>1630</v>
+        <v>1623</v>
       </c>
       <c r="X48" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Y48" t="n">
         <v>10</v>
@@ -12273,7 +12273,7 @@
         <v>352</v>
       </c>
       <c r="X51" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Y51" t="n">
         <v>-61</v>
@@ -12498,10 +12498,10 @@
         <v>0.044</v>
       </c>
       <c r="W52" t="n">
-        <v>5247</v>
+        <v>5237</v>
       </c>
       <c r="X52" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="Y52" t="n">
         <v>13</v>
@@ -12730,7 +12730,7 @@
         <v>0.234</v>
       </c>
       <c r="W53" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="X53" t="n">
         <v>14.6</v>
@@ -12959,13 +12959,13 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>0.231</v>
+        <v>0.23</v>
       </c>
       <c r="W54" t="n">
-        <v>1727</v>
+        <v>1735</v>
       </c>
       <c r="X54" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="Y54" t="n">
         <v>-3</v>
@@ -13197,7 +13197,7 @@
         <v>383</v>
       </c>
       <c r="X55" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="Y55" t="n">
         <v>246</v>
@@ -13652,10 +13652,10 @@
         <v>0.029</v>
       </c>
       <c r="W57" t="n">
-        <v>7481</v>
+        <v>7464</v>
       </c>
       <c r="X57" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="Y57" t="n">
         <v>25</v>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>0.245</v>
+        <v>0.246</v>
       </c>
       <c r="W58" t="n">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="X58" t="n">
-        <v>53.4</v>
+        <v>53.2</v>
       </c>
       <c r="Y58" t="n">
         <v>-4</v>
@@ -14109,13 +14109,13 @@
         </is>
       </c>
       <c r="V59" t="n">
-        <v>0.198</v>
+        <v>0.195</v>
       </c>
       <c r="W59" t="n">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="X59" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="Y59" t="n">
         <v>-1</v>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>0.298</v>
+        <v>0.294</v>
       </c>
       <c r="W61" t="n">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="X61" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Y61" t="n">
         <v>-66</v>
@@ -14808,10 +14808,10 @@
         <v>0.041</v>
       </c>
       <c r="W62" t="n">
-        <v>3275</v>
+        <v>3247</v>
       </c>
       <c r="X62" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="Y62" t="n">
         <v>-4</v>
@@ -15272,7 +15272,7 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>5296</v>
+        <v>5302</v>
       </c>
       <c r="X64" t="n">
         <v>12.4</v>
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="W65" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="X65" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="Y65" t="n">
         <v>118</v>
@@ -15961,10 +15961,10 @@
         </is>
       </c>
       <c r="V67" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="W67" t="n">
-        <v>3926</v>
+        <v>3867</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="n">
@@ -16191,13 +16191,13 @@
         </is>
       </c>
       <c r="V68" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="W68" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="X68" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="Y68" t="n">
         <v>-8</v>
@@ -16429,7 +16429,7 @@
         <v>257</v>
       </c>
       <c r="X69" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="Y69" t="n">
         <v>24</v>
@@ -16658,10 +16658,10 @@
         <v>0.034</v>
       </c>
       <c r="W70" t="n">
-        <v>1449</v>
+        <v>1429</v>
       </c>
       <c r="X70" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="Y70" t="n">
         <v>11</v>
@@ -16890,10 +16890,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>3455</v>
+        <v>3458</v>
       </c>
       <c r="X71" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="Y71" t="n">
         <v>5</v>
@@ -17122,7 +17122,7 @@
         <v>0.003</v>
       </c>
       <c r="W72" t="n">
-        <v>12877</v>
+        <v>12878</v>
       </c>
       <c r="X72" t="n">
         <v>41.1</v>
@@ -17354,7 +17354,7 @@
         <v>0.03</v>
       </c>
       <c r="W73" t="n">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="X73" t="n">
         <v>20.3</v>
@@ -17586,7 +17586,7 @@
         <v>0.053</v>
       </c>
       <c r="W74" t="n">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="n">
@@ -17816,10 +17816,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>3797</v>
+        <v>3822</v>
       </c>
       <c r="X75" t="n">
-        <v>85.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="Y75" t="n">
         <v>42</v>
@@ -18048,10 +18048,10 @@
         <v>0.006</v>
       </c>
       <c r="W76" t="n">
-        <v>4825</v>
+        <v>4828</v>
       </c>
       <c r="X76" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="Y76" t="n">
         <v>23</v>
@@ -18273,13 +18273,13 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="W77" t="n">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="X77" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
@@ -18496,7 +18496,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>30388</v>
+        <v>30412</v>
       </c>
       <c r="X78" t="n">
         <v>227</v>
@@ -18728,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>105258</v>
+        <v>105186</v>
       </c>
       <c r="X79" t="n">
         <v>30.3</v>
@@ -18957,10 +18957,10 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="W80" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="n">
@@ -19187,13 +19187,13 @@
         </is>
       </c>
       <c r="V81" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="W81" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="X81" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Y81" t="n">
         <v>21</v>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="W82" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="n">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mayur Uniquoters Ltd</t>
+          <t>MAYUR UNIQUOTERS LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
